--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Mistral-7B-Instruct-v0.3/default/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Mistral-7B-Instruct-v0.3/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D2">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="E2">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="G2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H3">
         <v>426</v>
